--- a/data/devices.xlsx
+++ b/data/devices.xlsx
@@ -1578,8 +1578,6 @@
           <t>未处理</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1878,8 +1876,6 @@
           <t>未处理</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1947,8 +1943,6 @@
           <t>未处理</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2247,8 +2241,6 @@
           <t>未处理</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2316,8 +2308,6 @@
           <t>未处理</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2385,8 +2375,6 @@
           <t>未处理</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2454,8 +2442,6 @@
           <t>未处理</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2677,8 +2663,6 @@
           <t>未处理</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3054,8 +3038,6 @@
           <t>未处理</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>[]</t>
